--- a/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Easthill_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Easthill_20251031.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>47.50</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>18.50</t>
         </is>
       </c>
     </row>
